--- a/Data/Home/Bathroom.HumanState.xlsx
+++ b/Data/Home/Bathroom.HumanState.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H389"/>
+  <dimension ref="A1:I391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709249205</v>
+        <v>1711841343</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709249926</v>
+        <v>1711841937</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709251523</v>
+        <v>1711844122</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709251964</v>
+        <v>1711844831</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709278284</v>
+        <v>1711877405</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709278680</v>
+        <v>1711877952</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709283962</v>
+        <v>1711898808</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709284715</v>
+        <v>1711899490</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709243749</v>
+        <v>1711926572</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709244200</v>
+        <v>1711927178</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709245261</v>
+        <v>1711928984</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709245780</v>
+        <v>1711929549</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709268877</v>
+        <v>1711962385</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709269242</v>
+        <v>1711962997</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709276474</v>
+        <v>1711971196</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709276974</v>
+        <v>1711973578</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709283097</v>
+        <v>1711975791</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709283572</v>
+        <v>1711977237</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709329389</v>
+        <v>1711979172</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709329916</v>
+        <v>1711979890</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709331035</v>
+        <v>1712014069</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709331531</v>
+        <v>1712014716</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709361362</v>
+        <v>1712018132</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709361896</v>
+        <v>1712018721</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709368135</v>
+        <v>1712050629</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709368710</v>
+        <v>1712052303</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1331,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709416178</v>
+        <v>1712058382</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709416749</v>
+        <v>1712058955</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709417708</v>
+        <v>1712059816</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709418174</v>
+        <v>1712060387</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709446399</v>
+        <v>1712100458</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709448056</v>
+        <v>1712101156</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709454081</v>
+        <v>1712102736</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709455370</v>
+        <v>1712103324</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709461943</v>
+        <v>1712139801</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1628,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709462499</v>
+        <v>1712141414</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1661,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709501683</v>
+        <v>1712141667</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709502118</v>
+        <v>1712142229</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709503381</v>
+        <v>1712145745</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1760,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709503898</v>
+        <v>1712147296</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709529697</v>
+        <v>1712148860</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709530200</v>
+        <v>1712149578</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1859,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709535487</v>
+        <v>1712186831</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709536033</v>
+        <v>1712187423</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709542309</v>
+        <v>1712189089</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709542929</v>
+        <v>1712189730</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709588082</v>
+        <v>1712218051</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709588645</v>
+        <v>1712218660</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709590116</v>
+        <v>1712220624</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709590670</v>
+        <v>1712221286</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709618599</v>
+        <v>1712224204</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709620109</v>
+        <v>1712225358</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709621498</v>
+        <v>1712226390</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709622503</v>
+        <v>1712226962</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709627686</v>
+        <v>1712273272</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709628837</v>
+        <v>1712273878</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709633524</v>
+        <v>1712277018</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709633923</v>
+        <v>1712277734</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2387,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709680001</v>
+        <v>1712308257</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709680984</v>
+        <v>1712308886</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709682117</v>
+        <v>1712316610</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2486,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709682582</v>
+        <v>1712317260</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709692230</v>
+        <v>1712323380</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709692743</v>
+        <v>1712324002</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2585,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709693271</v>
+        <v>1712363719</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2618,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709694209</v>
+        <v>1712365762</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709701506</v>
+        <v>1712367117</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709702402</v>
+        <v>1712367773</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2717,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709709028</v>
+        <v>1712381495</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2750,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709710062</v>
+        <v>1712383133</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2783,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709710433</v>
+        <v>1712392810</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709711747</v>
+        <v>1712394639</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2849,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709715935</v>
+        <v>1712399870</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2882,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709716396</v>
+        <v>1712400677</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2915,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709716478</v>
+        <v>1712402088</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709717141</v>
+        <v>1712402670</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +2981,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709765287</v>
+        <v>1712407976</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3014,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709766879</v>
+        <v>1712408626</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3047,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709768319</v>
+        <v>1712411831</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3080,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709768744</v>
+        <v>1712412414</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3113,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709769333</v>
+        <v>1712450037</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3146,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709770243</v>
+        <v>1712451687</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3179,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709777203</v>
+        <v>1712454136</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3212,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709777620</v>
+        <v>1712456504</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709786438</v>
+        <v>1712465692</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3278,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709786902</v>
+        <v>1712467391</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709788343</v>
+        <v>1712472740</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709788789</v>
+        <v>1712473396</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3377,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709792628</v>
+        <v>1712481050</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3410,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709793035</v>
+        <v>1712481645</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3443,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709795433</v>
+        <v>1712485453</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709796649</v>
+        <v>1712486028</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709796701</v>
+        <v>1712487316</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709797184</v>
+        <v>1712487920</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709799026</v>
+        <v>1712491257</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709799542</v>
+        <v>1712491832</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709800608</v>
+        <v>1712495874</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709801117</v>
+        <v>1712496410</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709804231</v>
+        <v>1712497437</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709804732</v>
+        <v>1712498922</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3773,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709848115</v>
+        <v>1712505507</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3806,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709848586</v>
+        <v>1712506200</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3839,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709851593</v>
+        <v>1712532080</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3872,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709851963</v>
+        <v>1712532809</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3905,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709873486</v>
+        <v>1712534564</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709873871</v>
+        <v>1712535140</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709879256</v>
+        <v>1712561325</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4004,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709879698</v>
+        <v>1712561975</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4037,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709883030</v>
+        <v>1712569255</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709883563</v>
+        <v>1712569836</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4103,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709935175</v>
+        <v>1712571438</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4136,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709935747</v>
+        <v>1712572011</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4169,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709937429</v>
+        <v>1712618637</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709937911</v>
+        <v>1712619205</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4235,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709964674</v>
+        <v>1712622998</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4268,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709965208</v>
+        <v>1712623623</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709967139</v>
+        <v>1712654793</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4334,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1709967663</v>
+        <v>1712656697</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1709972488</v>
+        <v>1712656977</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1709973500</v>
+        <v>1712657588</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1709974062</v>
+        <v>1712658842</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4466,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1709974654</v>
+        <v>1712660558</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4499,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710021336</v>
+        <v>1712668298</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710021885</v>
+        <v>1712668895</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710023133</v>
+        <v>1712705015</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4598,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710023593</v>
+        <v>1712705659</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4631,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710033845</v>
+        <v>1712707085</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4664,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710034846</v>
+        <v>1712707787</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4697,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710050769</v>
+        <v>1712744245</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4730,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710052021</v>
+        <v>1712744909</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4763,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710053545</v>
+        <v>1712745144</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4796,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710054020</v>
+        <v>1712746242</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4829,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710057893</v>
+        <v>1712754278</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4862,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710058371</v>
+        <v>1712755771</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4895,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710107082</v>
+        <v>1712763249</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4928,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710107538</v>
+        <v>1712763868</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4961,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710108475</v>
+        <v>1712790428</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +4994,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710108984</v>
+        <v>1712791101</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710128676</v>
+        <v>1712792926</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5060,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710129217</v>
+        <v>1712793543</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5093,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710135258</v>
+        <v>1712823590</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5126,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710135740</v>
+        <v>1712824240</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5159,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710150462</v>
+        <v>1712828585</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5192,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710150917</v>
+        <v>1712830973</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5225,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710195050</v>
+        <v>1712831882</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5258,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710195635</v>
+        <v>1712832545</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5291,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5310,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710197661</v>
+        <v>1712877113</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5324,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5343,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710198198</v>
+        <v>1712877670</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5357,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5376,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710225589</v>
+        <v>1712879041</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5390,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5409,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710227761</v>
+        <v>1712879672</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5423,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5442,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710234533</v>
+        <v>1712914955</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5456,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710236280</v>
+        <v>1712915627</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5489,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5508,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710242798</v>
+        <v>1712918444</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5522,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5541,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710243413</v>
+        <v>1712919148</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5555,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5574,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710289888</v>
+        <v>1712923369</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5588,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5607,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710290407</v>
+        <v>1712924021</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5621,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5640,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710291142</v>
+        <v>1712971566</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5654,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5673,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710292350</v>
+        <v>1712972208</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5687,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5706,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710300655</v>
+        <v>1712973205</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5720,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5739,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710301679</v>
+        <v>1712975671</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5753,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5772,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710306757</v>
+        <v>1712990348</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5786,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5805,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710307273</v>
+        <v>1712991038</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5819,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5838,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710310595</v>
+        <v>1712996544</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5852,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5871,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710311128</v>
+        <v>1712997105</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5885,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5904,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710313274</v>
+        <v>1712998987</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +5918,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5937,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710313749</v>
+        <v>1712999682</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +5951,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +5970,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710317572</v>
+        <v>1713005259</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +5984,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6003,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710318492</v>
+        <v>1713006122</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6017,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6036,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710320948</v>
+        <v>1713011175</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6050,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6069,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710322123</v>
+        <v>1713012871</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6083,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6102,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710322429</v>
+        <v>1713014083</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6116,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6135,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710322827</v>
+        <v>1713014677</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6149,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6168,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710324280</v>
+        <v>1713015387</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6182,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6201,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710324782</v>
+        <v>1713016090</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6215,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6234,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710326176</v>
+        <v>1713019242</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6248,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6267,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710326643</v>
+        <v>1713019876</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6281,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6300,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710329630</v>
+        <v>1713056834</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6314,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6333,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710330073</v>
+        <v>1713058368</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6347,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6366,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710371525</v>
+        <v>1713058597</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6380,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6399,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710373147</v>
+        <v>1713059248</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6413,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6432,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710374201</v>
+        <v>1713088725</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6446,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6465,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710374673</v>
+        <v>1713089414</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6479,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6498,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710386004</v>
+        <v>1713092979</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6512,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6531,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710387032</v>
+        <v>1713093588</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6545,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6564,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710391705</v>
+        <v>1713097286</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6578,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6597,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710392121</v>
+        <v>1713097950</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6611,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6630,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710394483</v>
+        <v>1713100397</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6644,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6663,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710395031</v>
+        <v>1713102041</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6677,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6696,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710400532</v>
+        <v>1713102450</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6710,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6729,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710401865</v>
+        <v>1713103133</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6743,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6762,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710402692</v>
+        <v>1713107849</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6776,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6795,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710403144</v>
+        <v>1713108553</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +6809,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6828,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710406218</v>
+        <v>1713137057</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +6842,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6861,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710406680</v>
+        <v>1713137646</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6875,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6894,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710407671</v>
+        <v>1713139060</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +6908,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6927,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710408115</v>
+        <v>1713139660</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +6941,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +6960,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710408901</v>
+        <v>1713168255</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +6974,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +6993,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710409440</v>
+        <v>1713168844</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7007,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7026,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710454921</v>
+        <v>1713175708</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7040,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7059,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710455408</v>
+        <v>1713176326</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7073,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7092,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710456770</v>
+        <v>1713185515</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7106,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7125,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710457372</v>
+        <v>1713186052</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7139,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7158,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710486830</v>
+        <v>1713223136</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7172,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7191,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710488286</v>
+        <v>1713223713</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7205,7 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7224,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710493400</v>
+        <v>1713225484</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7238,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7257,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710494920</v>
+        <v>1713226138</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7271,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7290,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710540004</v>
+        <v>1713258569</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7304,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7323,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710540497</v>
+        <v>1713259159</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7337,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7356,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710541311</v>
+        <v>1713263824</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7370,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7389,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710541712</v>
+        <v>1713264419</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7403,7 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7422,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710568085</v>
+        <v>1713266848</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7436,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7455,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710569306</v>
+        <v>1713267465</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7469,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7488,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710570624</v>
+        <v>1713274992</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7502,7 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7521,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710572129</v>
+        <v>1713276236</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7535,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7554,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710576314</v>
+        <v>1713277048</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7568,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7587,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710576804</v>
+        <v>1713279052</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,6 +7601,7 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7620,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710578231</v>
+        <v>1713309918</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7413,6 +7634,7 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7653,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710578839</v>
+        <v>1713310492</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7667,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7686,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710626104</v>
+        <v>1713313418</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7477,6 +7700,7 @@
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7719,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710626555</v>
+        <v>1713314045</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7509,6 +7733,7 @@
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7752,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710627724</v>
+        <v>1713346537</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +7766,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7785,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710628191</v>
+        <v>1713348471</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7573,6 +7799,7 @@
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7818,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710657214</v>
+        <v>1713349032</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7605,6 +7832,7 @@
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7851,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710657768</v>
+        <v>1713350838</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7865,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7884,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710660576</v>
+        <v>1713354301</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7669,6 +7898,7 @@
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +7917,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710661058</v>
+        <v>1713354928</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7701,6 +7931,7 @@
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +7950,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710712565</v>
+        <v>1713355084</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7733,6 +7964,7 @@
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +7983,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710713076</v>
+        <v>1713355724</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7765,6 +7997,7 @@
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8016,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710714621</v>
+        <v>1713395557</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7797,6 +8030,7 @@
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8049,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710715184</v>
+        <v>1713396273</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7829,6 +8063,7 @@
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8082,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710739717</v>
+        <v>1713397886</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7861,6 +8096,7 @@
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8115,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710740201</v>
+        <v>1713398561</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7893,6 +8129,7 @@
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8148,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710748174</v>
+        <v>1713438900</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8162,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8181,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710749805</v>
+        <v>1713439557</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7957,6 +8195,7 @@
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8214,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1710755649</v>
+        <v>1713440322</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7989,6 +8228,7 @@
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8247,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1710756256</v>
+        <v>1713440907</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8021,6 +8261,7 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8280,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1710798587</v>
+        <v>1713446685</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8053,6 +8294,7 @@
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8313,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1710799100</v>
+        <v>1713447280</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8085,6 +8327,7 @@
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8346,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1710800292</v>
+        <v>1713482203</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8117,6 +8360,7 @@
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8379,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1710800850</v>
+        <v>1713482844</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8149,6 +8393,7 @@
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8412,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1710830332</v>
+        <v>1713486709</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8181,6 +8426,7 @@
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8445,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1710830896</v>
+        <v>1713487226</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8213,6 +8459,7 @@
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8478,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1710835111</v>
+        <v>1713520979</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8245,6 +8492,7 @@
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8511,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1710835689</v>
+        <v>1713521668</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8525,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8544,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1710889467</v>
+        <v>1713529337</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8558,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8577,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1710890865</v>
+        <v>1713529877</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8341,6 +8591,7 @@
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8610,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1710900061</v>
+        <v>1713573600</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8373,6 +8624,7 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8643,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1710901864</v>
+        <v>1713575385</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8657,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8676,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1710903649</v>
+        <v>1713576829</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8437,6 +8690,7 @@
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8709,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1710904212</v>
+        <v>1713577488</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8469,6 +8723,7 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8742,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1710909874</v>
+        <v>1713591668</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8501,6 +8756,7 @@
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8775,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1710910377</v>
+        <v>1713593470</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8533,6 +8789,7 @@
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8808,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1710912256</v>
+        <v>1713601810</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8565,6 +8822,7 @@
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8841,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1710912808</v>
+        <v>1713602426</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8855,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +8874,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1710915920</v>
+        <v>1713604065</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8629,6 +8888,7 @@
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +8907,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1710916403</v>
+        <v>1713604653</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8661,6 +8921,7 @@
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +8940,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1710916769</v>
+        <v>1713607986</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8693,6 +8954,7 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8711,7 +8973,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1710917713</v>
+        <v>1713609239</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8725,6 +8987,7 @@
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8743,7 +9006,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1710919368</v>
+        <v>1713612150</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8757,6 +9020,7 @@
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8775,7 +9039,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1710920483</v>
+        <v>1713614045</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8789,6 +9053,7 @@
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8807,7 +9072,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1710921020</v>
+        <v>1713614954</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8821,6 +9086,7 @@
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8839,7 +9105,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1710921570</v>
+        <v>1713615668</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8853,6 +9119,7 @@
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8871,7 +9138,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1710922282</v>
+        <v>1713619617</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8885,6 +9152,7 @@
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8903,7 +9171,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1710922867</v>
+        <v>1713620221</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8917,6 +9185,7 @@
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8935,7 +9204,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1710924365</v>
+        <v>1713623589</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8949,6 +9218,7 @@
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8967,7 +9237,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1710924849</v>
+        <v>1713624195</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8981,6 +9251,7 @@
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8999,7 +9270,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1710928410</v>
+        <v>1713625625</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -9013,6 +9284,7 @@
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9031,7 +9303,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1710928862</v>
+        <v>1713626163</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9045,6 +9317,7 @@
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9063,7 +9336,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1710975400</v>
+        <v>1713658420</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9077,6 +9350,7 @@
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9095,7 +9369,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1710977186</v>
+        <v>1713659574</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9109,6 +9383,7 @@
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9127,7 +9402,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1710978057</v>
+        <v>1713662170</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -9141,6 +9416,7 @@
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9159,7 +9435,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1710980082</v>
+        <v>1713663737</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -9173,6 +9449,7 @@
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9191,7 +9468,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1710988373</v>
+        <v>1713665733</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -9205,6 +9482,7 @@
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9223,7 +9501,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1710989704</v>
+        <v>1713667276</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9237,6 +9515,7 @@
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9255,7 +9534,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1710991924</v>
+        <v>1713675588</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9269,6 +9548,7 @@
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9287,7 +9567,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1710992438</v>
+        <v>1713677558</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -9301,6 +9581,7 @@
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9319,7 +9600,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1710999412</v>
+        <v>1713682041</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9333,6 +9614,7 @@
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9351,7 +9633,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1710999938</v>
+        <v>1713682582</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -9365,6 +9647,7 @@
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9383,7 +9666,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1711000081</v>
+        <v>1713686811</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -9397,6 +9680,7 @@
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9415,7 +9699,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1711000564</v>
+        <v>1713688387</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -9429,6 +9713,7 @@
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9447,7 +9732,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1711004448</v>
+        <v>1713689649</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -9461,6 +9746,7 @@
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9479,7 +9765,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1711004799</v>
+        <v>1713690207</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -9493,6 +9779,7 @@
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9511,7 +9798,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1711006445</v>
+        <v>1713690677</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -9525,6 +9812,7 @@
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9543,7 +9831,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1711007008</v>
+        <v>1713692380</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -9557,6 +9845,7 @@
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9575,7 +9864,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1711007327</v>
+        <v>1713694883</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9589,6 +9878,7 @@
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9607,7 +9897,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1711009021</v>
+        <v>1713695466</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -9621,6 +9911,7 @@
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9639,7 +9930,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1711010948</v>
+        <v>1713696971</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9653,6 +9944,7 @@
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9671,7 +9963,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1711011439</v>
+        <v>1713697542</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9685,6 +9977,7 @@
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9703,7 +9996,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1711013752</v>
+        <v>1713700884</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9717,6 +10010,7 @@
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9735,7 +10029,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1711014334</v>
+        <v>1713702360</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9749,6 +10043,7 @@
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9767,7 +10062,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1711058350</v>
+        <v>1713702632</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9781,6 +10076,7 @@
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9799,7 +10095,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1711058904</v>
+        <v>1713703272</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9813,6 +10109,7 @@
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9831,7 +10128,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1711060516</v>
+        <v>1713706473</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9845,6 +10142,7 @@
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9863,7 +10161,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1711061064</v>
+        <v>1713707099</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9877,6 +10175,7 @@
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9895,7 +10194,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1711085654</v>
+        <v>1713707920</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9909,6 +10208,7 @@
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9927,7 +10227,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1711087116</v>
+        <v>1713708555</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9941,6 +10241,7 @@
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9959,7 +10260,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1711091054</v>
+        <v>1713740309</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9973,6 +10274,7 @@
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9991,7 +10293,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1711091428</v>
+        <v>1713740952</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -10005,6 +10307,7 @@
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10023,7 +10326,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1711092562</v>
+        <v>1713742848</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -10037,6 +10340,7 @@
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10055,7 +10359,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1711092952</v>
+        <v>1713743531</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -10069,6 +10373,7 @@
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10087,7 +10392,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1711098265</v>
+        <v>1713772258</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -10101,6 +10406,7 @@
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10119,7 +10425,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1711098761</v>
+        <v>1713772835</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -10133,6 +10439,7 @@
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10151,7 +10458,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1711144813</v>
+        <v>1713778237</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -10165,6 +10472,7 @@
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10183,7 +10491,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1711145400</v>
+        <v>1713779456</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -10197,6 +10505,7 @@
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10215,7 +10524,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1711146716</v>
+        <v>1713780013</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -10229,6 +10538,7 @@
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10247,7 +10557,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1711147287</v>
+        <v>1713780628</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -10261,6 +10571,7 @@
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10279,7 +10590,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1711169792</v>
+        <v>1713792261</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -10293,6 +10604,7 @@
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10311,7 +10623,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1711170239</v>
+        <v>1713792885</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -10325,6 +10637,7 @@
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10343,7 +10656,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1711173699</v>
+        <v>1713827805</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -10357,6 +10670,7 @@
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10375,7 +10689,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1711174144</v>
+        <v>1713828402</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -10389,6 +10703,7 @@
         </is>
       </c>
       <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10407,7 +10722,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1711175351</v>
+        <v>1713831692</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -10421,6 +10736,7 @@
         </is>
       </c>
       <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10439,7 +10755,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1711175725</v>
+        <v>1713832368</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -10453,6 +10769,7 @@
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10471,7 +10788,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1711182242</v>
+        <v>1713865636</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -10485,6 +10802,7 @@
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10503,7 +10821,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1711184038</v>
+        <v>1713866878</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -10517,6 +10835,7 @@
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10535,7 +10854,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1711232597</v>
+        <v>1713874434</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -10549,6 +10868,7 @@
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10567,7 +10887,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1711233139</v>
+        <v>1713875495</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -10581,6 +10901,7 @@
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10599,7 +10920,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1711235783</v>
+        <v>1713914443</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -10613,6 +10934,7 @@
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10631,7 +10953,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1711236378</v>
+        <v>1713915055</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -10645,6 +10967,7 @@
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10663,7 +10986,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1711268092</v>
+        <v>1713916486</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10677,6 +11000,7 @@
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10695,7 +11019,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1711268613</v>
+        <v>1713917084</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -10709,6 +11033,7 @@
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10727,7 +11052,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1711274008</v>
+        <v>1713943869</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10741,6 +11066,7 @@
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10759,7 +11085,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1711274481</v>
+        <v>1713944536</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10773,6 +11099,7 @@
         </is>
       </c>
       <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10791,7 +11118,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1711274673</v>
+        <v>1713952307</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10805,6 +11132,7 @@
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10823,7 +11151,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1711275213</v>
+        <v>1713952942</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10837,6 +11165,7 @@
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10855,7 +11184,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1711318935</v>
+        <v>1713962254</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -10869,6 +11198,7 @@
         </is>
       </c>
       <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10887,7 +11217,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1711319439</v>
+        <v>1713962829</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10901,6 +11231,7 @@
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10919,7 +11250,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1711322231</v>
+        <v>1714000724</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10933,6 +11264,7 @@
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10951,7 +11283,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1711322676</v>
+        <v>1714001325</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10965,6 +11297,7 @@
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10983,7 +11316,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1711343442</v>
+        <v>1714005305</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10997,6 +11330,7 @@
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11015,7 +11349,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1711344019</v>
+        <v>1714005871</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -11029,6 +11363,7 @@
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11047,7 +11382,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1711349977</v>
+        <v>1714034951</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -11061,6 +11396,7 @@
         </is>
       </c>
       <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11079,7 +11415,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1711350532</v>
+        <v>1714035584</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -11093,6 +11429,7 @@
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11111,7 +11448,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1711353486</v>
+        <v>1714037516</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -11125,6 +11462,7 @@
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11143,7 +11481,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1711355202</v>
+        <v>1714038773</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -11157,6 +11495,7 @@
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11175,7 +11514,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1711356523</v>
+        <v>1714042408</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -11189,6 +11528,7 @@
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11207,7 +11547,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1711358142</v>
+        <v>1714043056</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -11221,6 +11561,7 @@
         </is>
       </c>
       <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11239,7 +11580,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1711358877</v>
+        <v>1714052717</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -11253,6 +11594,7 @@
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11271,7 +11613,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1711360521</v>
+        <v>1714053293</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -11285,6 +11627,7 @@
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11303,7 +11646,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1711409508</v>
+        <v>1714086921</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -11317,6 +11660,7 @@
         </is>
       </c>
       <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11335,7 +11679,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1711410143</v>
+        <v>1714087502</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -11349,6 +11693,7 @@
         </is>
       </c>
       <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11367,7 +11712,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1711411863</v>
+        <v>1714089438</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -11381,6 +11726,7 @@
         </is>
       </c>
       <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11399,7 +11745,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1711412610</v>
+        <v>1714090039</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -11413,6 +11759,7 @@
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11431,7 +11778,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1711450957</v>
+        <v>1714127364</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -11445,6 +11792,7 @@
         </is>
       </c>
       <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11463,7 +11811,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1711452420</v>
+        <v>1714127960</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -11477,6 +11825,7 @@
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11495,7 +11844,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1711454290</v>
+        <v>1714129254</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -11509,6 +11858,7 @@
         </is>
       </c>
       <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11527,7 +11877,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1711454905</v>
+        <v>1714129850</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -11541,6 +11891,7 @@
         </is>
       </c>
       <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11559,7 +11910,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1711460112</v>
+        <v>1714137626</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -11573,6 +11924,7 @@
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11591,7 +11943,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1711460682</v>
+        <v>1714138257</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -11605,6 +11957,7 @@
         </is>
       </c>
       <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11623,7 +11976,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1711503302</v>
+        <v>1714177765</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -11637,6 +11990,7 @@
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11655,7 +12009,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1711504982</v>
+        <v>1714179195</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -11669,6 +12023,7 @@
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11687,7 +12042,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1711518510</v>
+        <v>1714181370</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -11701,6 +12056,7 @@
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11719,7 +12075,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1711520664</v>
+        <v>1714183496</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -11733,6 +12089,7 @@
         </is>
       </c>
       <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11751,7 +12108,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1711528934</v>
+        <v>1714197084</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -11765,6 +12122,7 @@
         </is>
       </c>
       <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11783,7 +12141,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1711529671</v>
+        <v>1714197718</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11797,6 +12155,7 @@
         </is>
       </c>
       <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11815,7 +12174,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1711530339</v>
+        <v>1714207625</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -11829,6 +12188,7 @@
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11847,7 +12207,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1711531030</v>
+        <v>1714208350</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -11861,6 +12221,7 @@
         </is>
       </c>
       <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11879,7 +12240,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1711539320</v>
+        <v>1714209605</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11893,6 +12254,7 @@
         </is>
       </c>
       <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11911,7 +12273,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1711539909</v>
+        <v>1714210270</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -11925,6 +12287,7 @@
         </is>
       </c>
       <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11943,7 +12306,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1711542013</v>
+        <v>1714212711</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -11957,6 +12320,7 @@
         </is>
       </c>
       <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11975,7 +12339,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1711544291</v>
+        <v>1714214767</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -11989,6 +12353,7 @@
         </is>
       </c>
       <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12007,7 +12372,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1711545550</v>
+        <v>1714217326</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -12021,6 +12386,7 @@
         </is>
       </c>
       <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12039,7 +12405,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1711546164</v>
+        <v>1714217918</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -12053,6 +12419,7 @@
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12071,7 +12438,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1711548074</v>
+        <v>1714220753</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -12085,6 +12452,7 @@
         </is>
       </c>
       <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12103,7 +12471,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1711548813</v>
+        <v>1714221422</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -12117,6 +12485,7 @@
         </is>
       </c>
       <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12135,7 +12504,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1711550469</v>
+        <v>1714224075</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -12149,6 +12518,7 @@
         </is>
       </c>
       <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12167,7 +12537,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1711551084</v>
+        <v>1714225476</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -12181,6 +12551,7 @@
         </is>
       </c>
       <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12199,7 +12570,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1711555495</v>
+        <v>1714226072</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -12213,6 +12584,7 @@
         </is>
       </c>
       <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12231,7 +12603,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1711556091</v>
+        <v>1714226673</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -12245,6 +12617,7 @@
         </is>
       </c>
       <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12263,7 +12636,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1711589782</v>
+        <v>1714231051</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -12277,6 +12650,7 @@
         </is>
       </c>
       <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12295,7 +12669,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1711591334</v>
+        <v>1714231678</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -12309,6 +12683,7 @@
         </is>
       </c>
       <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12327,7 +12702,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1711605901</v>
+        <v>1714231863</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -12341,6 +12716,7 @@
         </is>
       </c>
       <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12359,7 +12735,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1711607891</v>
+        <v>1714232570</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -12373,6 +12749,7 @@
         </is>
       </c>
       <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12391,7 +12768,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1711608116</v>
+        <v>1714268943</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -12405,6 +12782,7 @@
         </is>
       </c>
       <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12423,7 +12801,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1711608850</v>
+        <v>1714271071</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -12437,6 +12815,7 @@
         </is>
       </c>
       <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12455,7 +12834,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1711609127</v>
+        <v>1714271853</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -12469,6 +12848,7 @@
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12487,7 +12867,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1711609799</v>
+        <v>1714273753</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -12501,6 +12881,7 @@
         </is>
       </c>
       <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12519,7 +12900,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1711620764</v>
+        <v>1714282741</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -12533,6 +12914,7 @@
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12551,7 +12933,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1711621485</v>
+        <v>1714283472</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -12565,6 +12947,7 @@
         </is>
       </c>
       <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12583,7 +12966,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1711621834</v>
+        <v>1714290148</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -12597,6 +12980,7 @@
         </is>
       </c>
       <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -12615,7 +12999,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1711623590</v>
+        <v>1714290750</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -12629,6 +13013,7 @@
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12647,7 +13032,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1711624871</v>
+        <v>1714295218</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -12661,6 +13046,7 @@
         </is>
       </c>
       <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12679,7 +13065,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1711625498</v>
+        <v>1714295817</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -12693,6 +13079,7 @@
         </is>
       </c>
       <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12711,7 +13098,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1711630005</v>
+        <v>1714297104</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -12725,6 +13112,7 @@
         </is>
       </c>
       <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12743,7 +13131,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1711630654</v>
+        <v>1714298489</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -12757,6 +13145,7 @@
         </is>
       </c>
       <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12775,7 +13164,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1711634319</v>
+        <v>1714302346</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -12789,6 +13178,7 @@
         </is>
       </c>
       <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -12807,7 +13197,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1711635013</v>
+        <v>1714303491</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -12821,6 +13211,7 @@
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12839,7 +13230,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1711640400</v>
+        <v>1714306525</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -12853,6 +13244,7 @@
         </is>
       </c>
       <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12871,7 +13263,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1711641094</v>
+        <v>1714307763</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -12885,6 +13277,73 @@
         </is>
       </c>
       <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>1714312380</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Bathroom.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>1714313787</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Bathroom.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
